--- a/tools/importer/reports/import-listing-index.report.xlsx
+++ b/tools/importer/reports/import-listing-index.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="55">
   <si>
     <t>_reportFile</t>
   </si>
@@ -61,6 +61,24 @@
     <t>https://www.wknd-trendsetters.site/blog</t>
   </si>
   <si>
+    <t>case-studies.report.json</t>
+  </si>
+  <si>
+    <t>["columns-intro","columns-article"]</t>
+  </si>
+  <si>
+    <t>case-studies</t>
+  </si>
+  <si>
+    <t>2026-08-31T04:52:53.103Z</t>
+  </si>
+  <si>
+    <t>Inspiring Case Studies | Fashion Blog</t>
+  </si>
+  <si>
+    <t>https://www.wknd-trendsetters.site/case-studies</t>
+  </si>
+  <si>
     <t>faq.report.json</t>
   </si>
   <si>
@@ -82,6 +100,24 @@
     <t>https://www.wknd-trendsetters.site/faq</t>
   </si>
   <si>
+    <t>fashion-trends-of-the-season.report.json</t>
+  </si>
+  <si>
+    <t>fashion-trends-of-the-season</t>
+  </si>
+  <si>
+    <t>content-landing</t>
+  </si>
+  <si>
+    <t>2026-08-31T04:52:48.147Z</t>
+  </si>
+  <si>
+    <t>Top Fashion Trends for Young People | Fashion Blog</t>
+  </si>
+  <si>
+    <t>https://www.wknd-trendsetters.site/fashion-trends-of-the-season</t>
+  </si>
+  <si>
     <t>fashion-trends-young-adults-casual-sport.report.json</t>
   </si>
   <si>
@@ -94,7 +130,7 @@
     <t>cards-showcase</t>
   </si>
   <si>
-    <t>2026-08-30T16:59:51.294Z</t>
+    <t>2026-08-30T19:03:54.003Z</t>
   </si>
   <si>
     <t>Fashion Trends for Young Adults | Fashion Blog</t>
@@ -110,9 +146,6 @@
   </si>
   <si>
     <t>index</t>
-  </si>
-  <si>
-    <t>content-landing</t>
   </si>
   <si>
     <t>2026-08-30T17:00:20.576Z</t>
@@ -531,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
@@ -607,94 +640,146 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>27</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>28</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
         <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
         <v>33</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>34</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
         <v>37</v>
-      </c>
-      <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
         <v>40</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>41</v>
       </c>
-      <c r="G6" t="s">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>42</v>
       </c>
-      <c r="H6" t="s">
+      <c r="B7" t="s">
         <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
